--- a/entry_rater2.xlsx
+++ b/entry_rater2.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milic\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5B33C36-453F-49BA-A164-538C9488B6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E79DC7F-C0CE-4E48-A643-84DAC18C0C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-1140" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19305" yWindow="-1020" windowWidth="19410" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read me" sheetId="1" r:id="rId1"/>
     <sheet name="Part1" sheetId="2" r:id="rId2"/>
     <sheet name="Part2_OER" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="200">
   <si>
     <t>AccessTrap-CS annotation workbook (rater 2)</t>
   </si>
@@ -635,456 +635,6 @@
   </si>
   <si>
     <t>P2-30b</t>
-  </si>
-  <si>
-    <t>The example reverses the cost of search: 1 is at the root, and to reach 10 you have to go through the entire chain; I do not treat incorrect author names as SM.</t>
-  </si>
-  <si>
-    <t>A librarian who perfectly rearranges every shelf on every insertion suggests a complete rearrangement, instead of local maintenance of invariants.</t>
-  </si>
-  <si>
-    <t>Analogies equate dynamic typing with allowing invalid operations and static typing with complete safety; the time of checking is not the same as type safety.</t>
-  </si>
-  <si>
-    <t>The mutual exclusion example and the quiz confuse ordinary competition for a single resource with deadlock; merely waiting for an occupied resource is not enough.</t>
-  </si>
-  <si>
-    <t>The analogy correctly distinguishes fetching a search from following instructions to the next server.</t>
-  </si>
-  <si>
-    <t>Circular wait is well illustrated, but the claim that the entire system freezes unjustifiably extends a blockage of a set of processes to the entire system.</t>
-  </si>
-  <si>
-    <t>An index does not speed up only queries with few results: covering indexes and expression indexes are counterexamples to the claim that everything is always scanned.</t>
-  </si>
-  <si>
-    <t>The tickets faithfully represent a limited number of permits, waiting, and returning the permit; the omitted details do not change the described mechanism.</t>
-  </si>
-  <si>
-    <t>The middle position is a valid choice of pivot, but it is not the same as the mean; the explanation nevertheless recognizes the possibility of bad partitions.</t>
-  </si>
-  <si>
-    <t>Program size growth and the choice of richer output replace memory growth with input size and the time-space trade-off for the same task.</t>
-  </si>
-  <si>
-    <t>The claim that reference counting does not create large pauses ignores the cascading freeing of a large object graph.</t>
-  </si>
-  <si>
-    <t>The lack of a complete map does not mean that distance-vector cannot find shortest paths; link-state computation is performed by each router separately.</t>
-  </si>
-  <si>
-    <t>The teacher's and the task's immediate return conceals the actual time cost of saving and restoring the context.</t>
-  </si>
-  <si>
-    <t>The example with individual books shows all four conditions and a real circular wait; releasing resources breaks the blockage.</t>
-  </si>
-  <si>
-    <t>The example of keeping one's own toy with a permanent mutual wait faithfully illustrates deadlock; an incomplete list of conditions is not an error in itself.</t>
-  </si>
-  <si>
-    <t>Mark-and-sweep marks reachable objects, not garbage; the claim that reference counting leaves no unused objects ignores cycles.</t>
-  </si>
-  <si>
-    <t>The size of the box and the capacity of the container replace space complexity as a function of input size, without a correct representation of the time-space trade-off.</t>
-  </si>
-  <si>
-    <t>The precise rule allows a height difference of one; I take the expression perfectly balanced in the summary and absolute speed comparisons as imprecise shorthand.</t>
-  </si>
-  <si>
-    <t>Separate processes and execution units within a process are correctly distinguished; speedup using threads is not guaranteed for every task.</t>
-  </si>
-  <si>
-    <t>The musician and the additional activity represent execution within a process; details about shared memory are missing, but the analogy does not deny them.</t>
-  </si>
-  <si>
-    <t>The procedure suggests choosing only the neighbor of the current node instead of the globally smallest tentative distance and incorrectly excludes edges of weight zero.</t>
-  </si>
-  <si>
-    <t>An AVL may have a height difference of one; a perfectionist who corrects even the smallest difference creates a wrong invariant.</t>
-  </si>
-  <si>
-    <t>It equates static typing with safety, incorrectly allows assigning a string to an explicit number type in TypeScript, and incorrectly describes Java adding a number and a string.</t>
-  </si>
-  <si>
-    <t>Inheriting a property by itself does not guarantee LSP; substitutability is a requirement of preserving the contract, not an automatic consequence of an is-a relationship.</t>
-  </si>
-  <si>
-    <t>The dance analogy correctly distinguishes retaining matches and unmatched rows from the left, right, or both sides.</t>
-  </si>
-  <si>
-    <t>Reference counting does not guarantee the absence of pauses; the assignment pseudocode frees the old target before incrementing the new count, which is unsafe in self-assignment.</t>
-  </si>
-  <si>
-    <t>The analogies distinguish an unchanged final state from repeated addition; PUT should be read as repeating the same content on the same resource.</t>
-  </si>
-  <si>
-    <t>The unlimited claim that the CPU can execute only one program ignores multiple cores; the description of saving and restoring context is otherwise correct.</t>
-  </si>
-  <si>
-    <t>It incorrectly claims that the optimizer cannot combine OR searches and that a descending index is necessary for descending ORDER BY; several prohibitions on index use are overly general.</t>
-  </si>
-  <si>
-    <t>In the introduction, it presents Java/Python memory as occupied until explicit freeing, although automatic freeing is precisely the foundation of their GC.</t>
-  </si>
-  <si>
-    <t>Changing tasks while remembering the continuation point conveys the essence of context switching without claiming that the operation is free.</t>
-  </si>
-  <si>
-    <t>The gardener conveys the difference between stricter and looser balance maintenance; the fastest possible search is an exaggerated formulation, not a guaranteed property.</t>
-  </si>
-  <si>
-    <t>The conditions and their breaking are correctly stated; I read the formulation about not sharing resources in the context of at least one exclusive resource.</t>
-  </si>
-  <si>
-    <t>The number after the slash indicates the number of network bits, not the number of computers; Maple Street/20 directly suggests an incorrect meaning of the prefix.</t>
-  </si>
-  <si>
-    <t>OSPF is not without possible transient loops, and convergence is not guaranteed to be instantaneous or always shorter than a second.</t>
-  </si>
-  <si>
-    <t>The description of a constant small cost and real-time freeing in reference counting ignores cascades of freeing and their unbounded latency.</t>
-  </si>
-  <si>
-    <t>Static types do not remove all errors, and a dynamic system does not guess intent; the order-and-crust analogy mixes type checking with arbitrary choice.</t>
-  </si>
-  <si>
-    <t>The claim that mark-and-sweep is necessarily slower is not a general rule, and holding hands suggests undirected connection instead of directed reachability from roots.</t>
-  </si>
-  <si>
-    <t>Dijkstra allows zero weights; negative weights are not a synonym for shortcuts, and the restriction is not an inability to move backward.</t>
-  </si>
-  <si>
-    <t>Matches and the retention of unmatched rows are accurately shown; I interpret the empty place as a simplified representation of NULL, not as an empty string.</t>
-  </si>
-  <si>
-    <t>Counting pointers to zero and removing unmarked objects are correctly stated; details of roots and cycles are omitted without explicit denial.</t>
-  </si>
-  <si>
-    <t>All books on one shelf is not the same as low query selectivity; even within such a group, an index can efficiently find a rare value.</t>
-  </si>
-  <si>
-    <t>Marking retained objects and freeing at zero are correctly distinguished; I treat the lack of explicit transitive reachability as an omitted detail.</t>
-  </si>
-  <si>
-    <t>The probability of the worst sequence is not generally 1/n!, median-of-three does not exclude pathological inputs, and recursion space is not always O(log n).</t>
-  </si>
-  <si>
-    <t>Rearranging books by author describes a change of organization/indexing, not the deliberate introduction of redundant data that defines denormalization.</t>
-  </si>
-  <si>
-    <t>Grouping data is connected with explicitly mentioned duplication, additional space, and slower other operations; the analogy is rough, but does not deny redundancy.</t>
-  </si>
-  <si>
-    <t>DELETE is idempotent, a repeated identical PUT does not produce a new state each time, and POST may also process or modify existing data.</t>
-  </si>
-  <si>
-    <t>Tail recursion optimization generally does not reduce Quicksort to O(1) because of that; randomization and median-of-three do not guarantee avoiding the quadratic worst case.</t>
-  </si>
-  <si>
-    <t>It presents the removal of joins as automatically faster and instantaneous reading; the advantage of denormalization depends on the specific query and measured cost.</t>
-  </si>
-  <si>
-    <t>Distance-vector is not just a list of direct neighbors, OSPF also sends periodic refreshes, and link-state does not exclude all transient loops.</t>
-  </si>
-  <si>
-    <t>A small table or repeated values are not sufficient for an index to always be useless; the selectivity of the specific query and the cost of the plan matter.</t>
-  </si>
-  <si>
-    <t>Reference counting is not a single-pass algorithm; it updates counters during execution and can cascade-free objects, so comparing speed by number of passes is not valid.</t>
-  </si>
-  <si>
-    <t>The second paragraph explicitly states duplication for faster reading and additional work with copies, which clarifies the initial gluing of cards.</t>
-  </si>
-  <si>
-    <t>The banker's algorithm serves to avoid unsafe states, and is not an example of requesting all resources at once in order to break the hold-and-wait condition.</t>
-  </si>
-  <si>
-    <t>The CIDR number of bits and the /24 example are correct; I read the device address as beginner shorthand for the address of a network interface.</t>
-  </si>
-  <si>
-    <t>Sorting toys and notebooks does not represent atomicity, full functional dependencies, and removal of transitive dependencies; the rules of normal forms are incorrectly replaced.</t>
-  </si>
-  <si>
-    <t>It correctly distinguishes the isolated address space of a process from shared resources and the separate context of threads; cost and isolation estimates are typical, not absolute.</t>
-  </si>
-  <si>
-    <t>The tallest student does not give a balanced split, and when choosing the shortest, almost all the others go into the higher group; it also confuses the number of levels with the total number of splits.</t>
-  </si>
-  <si>
-    <t>The difference in responsibility for finding the answer is correct; the description of efficiency and safety is general, but does not change the resolution mechanism.</t>
-  </si>
-  <si>
-    <t>A semaphore is not just a number, nor is synchronization just obedience to a number; viewing the number and decrementing separately without an atomic acquire is not safe synchronization.</t>
-  </si>
-  <si>
-    <t>Separate stores and workers sharing common resources correctly convey the basic difference between processes and threads.</t>
-  </si>
-  <si>
-    <t>Toy boxes, parts, and instructions are arbitrarily identified with 1NF, 2NF, and 3NF, instead of representing their different conditions about values and dependencies.</t>
-  </si>
-  <si>
-    <t>Copying for fewer joins and additional work on changes are correctly described; the quiz does not provide enough workload for an unambiguous choice.</t>
-  </si>
-  <si>
-    <t>POSIX sem_wait does not require a negative counter, and two empty/full semaphores do not guarantee mutual exclusion with multiple producers or consumers.</t>
-  </si>
-  <si>
-    <t>The claim that threads share absolutely everything erases their separate stack, registers, and program counter; a shared kitchen alone does not show that boundary.</t>
-  </si>
-  <si>
-    <t>Merging the Products and Prices tables into Items is not necessarily denormalization: without introduced redundancy, the result can remain normalized.</t>
-  </si>
-  <si>
-    <t>The claim that all routers immediately learn about a closed road removes change detection, LSA message transmission, and convergence time.</t>
-  </si>
-  <si>
-    <t>OSPF does not receive the whole map from every router but advertisements of local links; RIP is not guessing but a distributed distance computation.</t>
-  </si>
-  <si>
-    <t>The analogy promises an immediately correct path even when links change, without time for detecting the change and exchanging information.</t>
-  </si>
-  <si>
-    <t>The general claim that mark-and-sweep is slower replaces the cost-latency trade-off with a universal speed ordering; the mechanisms are otherwise faithfully presented.</t>
-  </si>
-  <si>
-    <t>The mask as a divider and the relationship of prefix length to subnet size are accurately shown; claims about traffic are simplified.</t>
-  </si>
-  <si>
-    <t>Zero weights and the reason for the finiteness of distance are correctly stated; the awkward order of presenting the example does not change the presented counterexample.</t>
-  </si>
-  <si>
-    <t>It confuses the time and memory of brute-force TSP and describes O(n log n) as logarithmic memory growth; the number of total recursive calls is not peak occupied memory.</t>
-  </si>
-  <si>
-    <t>The rule always subtract two addresses is not universal: /31 point-to-point and /32 have special semantics, although the /24 example is correct.</t>
-  </si>
-  <si>
-    <t>Identifying INNER/FULL JOIN with set intersection/union ignores column joining, the match condition, and multiple matches in SQL.</t>
-  </si>
-  <si>
-    <t>Recursive resolution is not necessarily faster; the difference is who follows queries and recommendations, and speed depends on cache and network.</t>
-  </si>
-  <si>
-    <t>One bad pivot choice does not by itself create a quadratic case; the analogy of the average case with constant perfect halving is also too narrow.</t>
-  </si>
-  <si>
-    <t>The network-host divider and the relationship of short and long prefixes to block size are accurately shown.</t>
-  </si>
-  <si>
-    <t>Outdated statistics are not an outdated or unmaintained index; indexes are maintained on writes, and statistics affect plan choice, not index validity.</t>
-  </si>
-  <si>
-    <t>Floors as subnets within a single IP address suggest the opposite relationship: a subnet is a block of addresses, and an individual address is not a container of subnets.</t>
-  </si>
-  <si>
-    <t>Idempotency means the same intended effect on state, not necessarily the same response; POST is not obliged to create a new resource on every repetition.</t>
-  </si>
-  <si>
-    <t>It incorrectly contrasts thread management in the kernel with process management in user libraries; user threads also exist, and processes are managed by the OS.</t>
-  </si>
-  <si>
-    <t>A small table and retrieving most of the data are valid reasons for scanning; the expression proper use of an index is imprecise, but is not a new algorithmic requirement.</t>
-  </si>
-  <si>
-    <t>The key analogy reverses the direction of LSP: code that requests a subtype does not have to accept a supertype, rather the subtype must fulfill the contract that the client expects from the supertype.</t>
-  </si>
-  <si>
-    <t>The introductory rules of normal forms and the trade-offs correspond to the reference description; formulations about only the primary key simplify the formal role of candidate keys.</t>
-  </si>
-  <si>
-    <t>It correctly connects the levels of recursion and partition sizes with average O(n log n) and worst O(n²), without a guarantee of perfect balance.</t>
-  </si>
-  <si>
-    <t>AVL requires a height difference of at most one, not exactly equal heights; the analogy of a perfectly level seesaw directly confirms the wrong rule.</t>
-  </si>
-  <si>
-    <t>The text claims that Square inherits Rectangle, but the code inherits Shape; the example therefore does not implement the stated hierarchy, although it illustrates the violation of the setter contract well.</t>
-  </si>
-  <si>
-    <t>Reachability, cycles, and zero reference count are correctly separated; I read the claims about low latency as typical behavior, not a strict guarantee.</t>
-  </si>
-  <si>
-    <t>The janitor marks garbage and removes what is marked, which reverses mark-and-sweep: reachable objects are marked, and unmarked ones are removed.</t>
-  </si>
-  <si>
-    <t>The analogy of permits, waiting, and returning a ticket does not introduce a new error compared to the standard.</t>
-  </si>
-  <si>
-    <t>The new reduction of a semaphore to just a number and of synchronization to tracking that number removes the atomic operation that the standard explicitly describes.</t>
-  </si>
-  <si>
-    <t>The slower/faster ordering is already suggested by the comparison in the standard; the model of the counter, roots, and mark propagation is not broken by a new simplification.</t>
-  </si>
-  <si>
-    <t>Holding hands introduces mutual connection as a criterion, while the standard describes following directed references from roots; the assessment of the analogy is questionable.</t>
-  </si>
-  <si>
-    <t>Instead of marking reachable objects and removing unmarked ones, garbage is marked for removal; additionally, it is wrongly promised that nothing will remain unused for long.</t>
-  </si>
-  <si>
-    <t>Spraying paint on garbage and removing it reverses the meaning of the mark in the mark-and-sweep procedure, which the standard does not do.</t>
-  </si>
-  <si>
-    <t>Outdated statistics from the standard have been turned into an outdated/unmaintained index that cannot be used; these are different mechanisms.</t>
-  </si>
-  <si>
-    <t>The new exclusive rule that an index speeds up only the retrieval of a small number of rows excludes, for example, a useful covering index; the standard says that this is the most favorable, not the only case.</t>
-  </si>
-  <si>
-    <t>Confusing static/dynamic typing with stricter/weaker safety already exists in the standard, so there is no new OER for that error.</t>
-  </si>
-  <si>
-    <t>The chef who arbitrarily guesses a dish and the static menu without any errors introduce claims that dynamic types guess intent and that static types remove all errors.</t>
-  </si>
-  <si>
-    <t>Shared route computation and a direct path replace the individual SPF computation and iterative distance determination from the standard.</t>
-  </si>
-  <si>
-    <t>A claim has been added about instantly finding the correct path even after roads change; the standard does not give such a guarantee of the absence of convergence.</t>
-  </si>
-  <si>
-    <t>The size of boxes and their capacity replace the growth of required memory with input size; the standard nevertheless states that relationship.</t>
-  </si>
-  <si>
-    <t>Program growth and the choice of a different, richer task replace input size and the time-space trade-off for the same problem.</t>
-  </si>
-  <si>
-    <t>The claim that reference counting is fast because it needs only one pass is a new error; the standard describes constant updating of references, not one pass.</t>
-  </si>
-  <si>
-    <t>The basic difference between mark-and-sweep and count-to-zero is preserved; the general instantaneous availability of freeing is already exaggerated in the standard.</t>
-  </si>
-  <si>
-    <t>Rearranging every shelf on every book arrival adds a wrong global update mechanism, unlike rotations and recoloring in the standard.</t>
-  </si>
-  <si>
-    <t>The claim that even the smallest height difference is corrected is a new concretized error: the standard explicitly allows a difference of one, despite the hyperbole in the summary.</t>
-  </si>
-  <si>
-    <t>The number after the slash is presented as the number of computers/houses, while the standard correctly determines it as the number of network bits.</t>
-  </si>
-  <si>
-    <t>Floors as subnets within a single address reverse the relationship between subnets and addresses; the standard presents a subnet as a group of addresses.</t>
-  </si>
-  <si>
-    <t>The example with a single controller and the quiz introduce an identification of ordinary conflict over an occupied resource with deadlock; the standard requires all four conditions.</t>
-  </si>
-  <si>
-    <t>A blockage of part of the processes has been turned into a freezing of the entire system, which the standard does not claim.</t>
-  </si>
-  <si>
-    <t>Duplication, avoiding joins, and additional work on changes remain recognizable; exaggerated promises of speed already exist in the standard.</t>
-  </si>
-  <si>
-    <t>The later part explicitly explains duplication and maintenance of additional copies, so the initial gluing of cards does not introduce a separate false definition.</t>
-  </si>
-  <si>
-    <t>Separate processes and helpers within a process retain the basic relationship; details of the private context are omitted, but are not denied.</t>
-  </si>
-  <si>
-    <t>An additional activity of the same musician represents execution within a process; omitting memory details is not in itself a new error.</t>
-  </si>
-  <si>
-    <t>It correctly separates the person who searches on someone else's behalf from independently following recommendations; it does not claim an unconditional speed advantage.</t>
-  </si>
-  <si>
-    <t>A categorical claim has been added that the recursive method is faster; the standard speaks of less work for the client, not of guaranteed lower latency.</t>
-  </si>
-  <si>
-    <t>A repeated identical PUT and DELETE are presented with the same final state, and POST with repeated addition; there is no new error.</t>
-  </si>
-  <si>
-    <t>DELETE is wrongly declared non-idempotent, and PUT as an addition that changes state every time; the standard correctly distinguishes these properties.</t>
-  </si>
-  <si>
-    <t>Remembering the continuation point and shifting attention retain the basic mechanism; the analogy does not claim that switching has no cost.</t>
-  </si>
-  <si>
-    <t>It twice promises an instantaneous return to the task, although the standard explicitly emphasizes the time cost of saving and restoring the context.</t>
-  </si>
-  <si>
-    <t>Substitutability is presented as an automatic consequence of inheriting a common property, while in the standard LSP is a requirement of preserving the contract.</t>
-  </si>
-  <si>
-    <t>The key and lock reverse the direction of substitutability: a client of the subtype is not obliged to accept the supertype, rather the subtype must be usable in place of the supertype.</t>
-  </si>
-  <si>
-    <t>Non-negative weights have been turned into strictly positive ones; the new analogy wrongly prohibits edges of zero weight as well.</t>
-  </si>
-  <si>
-    <t>It explicitly excludes zero weight and suggests local choice of the neighbor of the current city instead of the global minimum of tentative distances.</t>
-  </si>
-  <si>
-    <t>The middle position is one permitted choice of pivot, and possible bad partitions are still stated; there is no new essential error.</t>
-  </si>
-  <si>
-    <t>Repeated partitioning and both orders of time complexity are preserved; a typical, not guaranteed, improvement of pivot choice is already stated by the standard.</t>
-  </si>
-  <si>
-    <t>The stricter and looser gardener convey the same trade-off; exaggerating perfect balance and optimal speed already exists in the standard.</t>
-  </si>
-  <si>
-    <t>Explicitly equal heights is a new wrong rule, because the standard, along with its imprecisions, still states the permitted factors -1, 0, and 1.</t>
-  </si>
-  <si>
-    <t>The separation of the network and host part and the relationship between mask length and block size are faithfully preserved.</t>
-  </si>
-  <si>
-    <t>The mask as the marked network part and more remaining host bits with a shorter prefix do not introduce a new error.</t>
-  </si>
-  <si>
-    <t>The match conditions and retention of unmatched rows are preserved; the empty place is an everyday representation of a missing value, not a claim about an empty string.</t>
-  </si>
-  <si>
-    <t>The dance analogy correctly distinguishes preserved sides without an explicit restriction to one match per row; missing details are not an error in themselves.</t>
-  </si>
-  <si>
-    <t>In the concrete example, each resource has one copy and a closed waiting cycle is shown; the claim about a blockage of that example does not introduce general sufficiency of all four conditions.</t>
-  </si>
-  <si>
-    <t>The mutual holding of toys and permanent waiting illustrate circular blockage; the omitted formal list of conditions does not change the concrete example.</t>
-  </si>
-  <si>
-    <t>The examples of a small table and retrieving most of the data follow the standard, without a new technical claim that changes the mechanism.</t>
-  </si>
-  <si>
-    <t>Placing all books on one shelf is a new replacement for selectivity: physical grouping alone does not make an index useless.</t>
-  </si>
-  <si>
-    <t>The claim about the absence of large pauses in reference counting is already in the standard; the manner of marking and the cycle limitation remain the same.</t>
-  </si>
-  <si>
-    <t>Marking retained objects and removing at zero remain correct; the lack of details about roots and cycles does not introduce an explicitly new false claim.</t>
-  </si>
-  <si>
-    <t>The tallest student wrongly gives a balanced split, and seven levels for 100 elements is confused with seven total splits; these are not errors of the standard.</t>
-  </si>
-  <si>
-    <t>The final claim that one bad pivot choice ruins everything is a new error: a quadratic worst case requires a sufficiently long series of bad partitions.</t>
-  </si>
-  <si>
-    <t>The claim that everyone immediately learns about a link closure removes the time of detection and propagation; the standard's fast recalculation after a base change is not instantaneous global knowledge.</t>
-  </si>
-  <si>
-    <t>Receiving the whole map from every router replaces the exchange of local link advertisements from the standard; RIP is additionally reduced to guessing.</t>
-  </si>
-  <si>
-    <t>The claim that threads share absolutely everything removes the separate stack and program counter that the standard explicitly distinguishes from shared resources.</t>
-  </si>
-  <si>
-    <t>Separate stores and a shared kitchen within a store represent the basic relationship without an explicit claim that threads also share the private execution context.</t>
-  </si>
-  <si>
-    <t>Unlike mere rearranging, the text explicitly retains duplication, additional space, and a trade-off with other operations; there is no separate new error.</t>
-  </si>
-  <si>
-    <t>Rearranging books by author instead of subject replaces deliberate redundancy with a change in the manner of organization/indexing.</t>
-  </si>
-  <si>
-    <t>Atomicity and functional dependencies have been replaced by categories of toys and arbitrary rules about notebooks, which do not exist in the standard.</t>
-  </si>
-  <si>
-    <t>Toy boxes, parts, and instructions become definitions of 1NF, 2NF, and 3NF, thereby introducing non-existent rules instead of the conditions from the standard.</t>
   </si>
 </sst>
 </file>
@@ -1202,7 +752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1224,7 +774,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1737,7 +1286,7 @@
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="188.21875" style="11" customWidth="1"/>
+    <col min="5" max="5" width="73.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1762,68 +1311,60 @@
         <v>48</v>
       </c>
       <c r="B2" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="9">
         <v>0</v>
       </c>
       <c r="D2" s="9">
-        <v>3</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>200</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E2" s="10"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B3" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="9">
-        <v>3</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>201</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B4" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="9">
         <v>1</v>
       </c>
       <c r="D4" s="9">
-        <v>2</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>202</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B5" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="9">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>203</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -1836,11 +1377,9 @@
         <v>0</v>
       </c>
       <c r="D6" s="9">
-        <v>5</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>204</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -1855,26 +1394,22 @@
       <c r="D7" s="9">
         <v>3</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>205</v>
-      </c>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="9">
-        <v>3</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>206</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -1887,62 +1422,54 @@
         <v>0</v>
       </c>
       <c r="D9" s="9">
-        <v>5</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>207</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B10" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="9">
         <v>0</v>
       </c>
       <c r="D10" s="9">
-        <v>4</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>208</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B11" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="9">
         <v>3</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>209</v>
-      </c>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="9">
         <v>0</v>
       </c>
       <c r="D12" s="9">
-        <v>3</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>210</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
@@ -1952,31 +1479,27 @@
         <v>1</v>
       </c>
       <c r="C13" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="9">
         <v>3</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>211</v>
-      </c>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="9">
-        <v>3</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>212</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
@@ -1991,26 +1514,22 @@
       <c r="D15" s="9">
         <v>5</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>213</v>
-      </c>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B16" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="9">
         <v>0</v>
       </c>
       <c r="D16" s="9">
-        <v>5</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>214</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
@@ -2020,31 +1539,27 @@
         <v>1</v>
       </c>
       <c r="C17" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="9">
         <v>2</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>215</v>
-      </c>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" s="9">
         <v>1</v>
       </c>
       <c r="D18" s="9">
-        <v>1</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>216</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
@@ -2057,11 +1572,9 @@
         <v>0</v>
       </c>
       <c r="D19" s="9">
-        <v>4</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>217</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
@@ -2076,77 +1589,67 @@
       <c r="D20" s="9">
         <v>4</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>218</v>
-      </c>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B21" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="9">
         <v>0</v>
       </c>
       <c r="D21" s="9">
-        <v>4</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>219</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="9">
-        <v>2</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>220</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B23" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="9">
-        <v>2</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>221</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="9">
-        <v>2</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>222</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
@@ -2156,14 +1659,12 @@
         <v>1</v>
       </c>
       <c r="C25" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="9">
         <v>3</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>223</v>
-      </c>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
@@ -2176,28 +1677,24 @@
         <v>0</v>
       </c>
       <c r="D26" s="9">
-        <v>5</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>224</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B27" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="9">
         <v>0</v>
       </c>
       <c r="D27" s="9">
-        <v>3</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>225</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
@@ -2212,60 +1709,52 @@
       <c r="D28" s="9">
         <v>4</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>226</v>
-      </c>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>75</v>
       </c>
       <c r="B29" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" s="9">
         <v>0</v>
       </c>
       <c r="D29" s="9">
-        <v>3</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>227</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" s="9">
         <v>0</v>
       </c>
       <c r="D30" s="9">
-        <v>2</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>228</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B31" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" s="9">
         <v>0</v>
       </c>
       <c r="D31" s="9">
-        <v>3</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>229</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
@@ -2278,11 +1767,9 @@
         <v>0</v>
       </c>
       <c r="D32" s="9">
-        <v>5</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>230</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
@@ -2297,9 +1784,7 @@
       <c r="D33" s="9">
         <v>4</v>
       </c>
-      <c r="E33" s="10" t="s">
-        <v>231</v>
-      </c>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
@@ -2312,18 +1797,16 @@
         <v>0</v>
       </c>
       <c r="D34" s="9">
-        <v>4</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>232</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E34" s="10"/>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B35" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" s="9">
         <v>1</v>
@@ -2331,94 +1814,82 @@
       <c r="D35" s="9">
         <v>2</v>
       </c>
-      <c r="E35" s="10" t="s">
-        <v>233</v>
-      </c>
+      <c r="E35" s="10"/>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>82</v>
       </c>
       <c r="B36" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" s="9">
         <v>0</v>
       </c>
       <c r="D36" s="9">
-        <v>3</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>234</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E36" s="10"/>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B37" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" s="9">
         <v>0</v>
       </c>
       <c r="D37" s="9">
-        <v>3</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>235</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E37" s="10"/>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B38" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="9">
         <v>1</v>
       </c>
       <c r="D38" s="9">
-        <v>2</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>236</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E38" s="10"/>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>85</v>
       </c>
       <c r="B39" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="9">
-        <v>3</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>237</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E39" s="10"/>
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B40" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="9">
-        <v>2</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>238</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E40" s="10"/>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
@@ -2431,11 +1902,9 @@
         <v>0</v>
       </c>
       <c r="D41" s="9">
-        <v>4</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>239</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E41" s="10"/>
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
@@ -2450,26 +1919,22 @@
       <c r="D42" s="9">
         <v>4</v>
       </c>
-      <c r="E42" s="10" t="s">
-        <v>240</v>
-      </c>
+      <c r="E42" s="10"/>
     </row>
     <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>89</v>
       </c>
       <c r="B43" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="9">
-        <v>3</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>241</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E43" s="10"/>
     </row>
     <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
@@ -2484,60 +1949,52 @@
       <c r="D44" s="9">
         <v>4</v>
       </c>
-      <c r="E44" s="10" t="s">
-        <v>242</v>
-      </c>
+      <c r="E44" s="10"/>
     </row>
     <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B45" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45" s="9">
         <v>0</v>
       </c>
       <c r="D45" s="9">
-        <v>3</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>243</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E45" s="10"/>
     </row>
     <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>92</v>
       </c>
       <c r="B46" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" s="9">
-        <v>2</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>244</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E46" s="10"/>
     </row>
     <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B47" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" s="9">
         <v>0</v>
       </c>
       <c r="D47" s="9">
-        <v>4</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>245</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E47" s="10"/>
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
@@ -2547,99 +2004,87 @@
         <v>1</v>
       </c>
       <c r="C48" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" s="9">
         <v>2</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>246</v>
-      </c>
+      <c r="E48" s="10"/>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>95</v>
       </c>
       <c r="B49" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" s="9">
         <v>0</v>
       </c>
       <c r="D49" s="9">
-        <v>3</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>247</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E49" s="10"/>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>96</v>
       </c>
       <c r="B50" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="9">
         <v>0</v>
       </c>
       <c r="D50" s="9">
-        <v>3</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>248</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E50" s="10"/>
     </row>
     <row r="51" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B51" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" s="9">
         <v>0</v>
       </c>
       <c r="D51" s="9">
-        <v>3</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>249</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E51" s="10"/>
     </row>
     <row r="52" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B52" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="9">
         <v>0</v>
       </c>
       <c r="D52" s="9">
-        <v>3</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>250</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E52" s="10"/>
     </row>
     <row r="53" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B53" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" s="9">
-        <v>2</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>251</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E53" s="10"/>
     </row>
     <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
@@ -2652,28 +2097,24 @@
         <v>0</v>
       </c>
       <c r="D54" s="9">
-        <v>4</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>252</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E54" s="10"/>
     </row>
     <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B55" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" s="9">
         <v>0</v>
       </c>
       <c r="D55" s="9">
-        <v>3</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>253</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E55" s="10"/>
     </row>
     <row r="56" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
@@ -2686,11 +2127,9 @@
         <v>0</v>
       </c>
       <c r="D56" s="9">
-        <v>4</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>254</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E56" s="10"/>
     </row>
     <row r="57" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
@@ -2700,14 +2139,12 @@
         <v>1</v>
       </c>
       <c r="C57" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" s="9">
-        <v>1</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>255</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E57" s="10"/>
     </row>
     <row r="58" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
@@ -2720,28 +2157,24 @@
         <v>0</v>
       </c>
       <c r="D58" s="9">
-        <v>4</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>256</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E58" s="10"/>
     </row>
     <row r="59" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B59" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" s="9">
-        <v>2</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>257</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E59" s="10"/>
     </row>
     <row r="60" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
@@ -2756,26 +2189,22 @@
       <c r="D60" s="9">
         <v>4</v>
       </c>
-      <c r="E60" s="10" t="s">
-        <v>258</v>
-      </c>
+      <c r="E60" s="10"/>
     </row>
     <row r="61" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B61" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" s="9">
-        <v>2</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>259</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E61" s="10"/>
     </row>
     <row r="62" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
@@ -2788,11 +2217,9 @@
         <v>0</v>
       </c>
       <c r="D62" s="9">
-        <v>5</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>260</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E62" s="10"/>
     </row>
     <row r="63" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
@@ -2802,14 +2229,12 @@
         <v>1</v>
       </c>
       <c r="C63" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" s="9">
         <v>2</v>
       </c>
-      <c r="E63" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="E63" s="10"/>
     </row>
     <row r="64" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
@@ -2824,128 +2249,112 @@
       <c r="D64" s="9">
         <v>4</v>
       </c>
-      <c r="E64" s="10" t="s">
-        <v>262</v>
-      </c>
+      <c r="E64" s="10"/>
     </row>
     <row r="65" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B65" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" s="9">
         <v>0</v>
       </c>
       <c r="D65" s="9">
-        <v>3</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>263</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E65" s="10"/>
     </row>
     <row r="66" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B66" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66" s="9">
-        <v>3</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>264</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E66" s="10"/>
     </row>
     <row r="67" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>113</v>
       </c>
       <c r="B67" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C67" s="9">
         <v>0</v>
       </c>
       <c r="D67" s="9">
-        <v>3</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>265</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E67" s="10"/>
     </row>
     <row r="68" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B68" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" s="9">
-        <v>3</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>266</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E68" s="10"/>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B69" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" s="9">
-        <v>2</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>267</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E69" s="10"/>
     </row>
     <row r="70" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>116</v>
       </c>
       <c r="B70" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70" s="9">
-        <v>3</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>268</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E70" s="10"/>
     </row>
     <row r="71" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B71" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71" s="9">
         <v>0</v>
       </c>
       <c r="D71" s="9">
-        <v>3</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>269</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E71" s="10"/>
     </row>
     <row r="72" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
@@ -2960,9 +2369,7 @@
       <c r="D72" s="9">
         <v>4</v>
       </c>
-      <c r="E72" s="10" t="s">
-        <v>270</v>
-      </c>
+      <c r="E72" s="10"/>
     </row>
     <row r="73" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
@@ -2977,94 +2384,82 @@
       <c r="D73" s="9">
         <v>4</v>
       </c>
-      <c r="E73" s="10" t="s">
-        <v>271</v>
-      </c>
+      <c r="E73" s="10"/>
     </row>
     <row r="74" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B74" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74" s="9">
         <v>0</v>
       </c>
       <c r="D74" s="9">
-        <v>2</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>272</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E74" s="10"/>
     </row>
     <row r="75" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B75" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" s="9">
         <v>0</v>
       </c>
       <c r="D75" s="9">
-        <v>3</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>273</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E75" s="10"/>
     </row>
     <row r="76" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B76" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C76" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76" s="9">
-        <v>3</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>274</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E76" s="10"/>
     </row>
     <row r="77" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B77" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C77" s="9">
         <v>0</v>
       </c>
       <c r="D77" s="9">
-        <v>3</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>275</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E77" s="10"/>
     </row>
     <row r="78" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B78" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" s="9">
-        <v>3</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>276</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E78" s="10"/>
     </row>
     <row r="79" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
@@ -3077,79 +2472,69 @@
         <v>0</v>
       </c>
       <c r="D79" s="9">
-        <v>5</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>277</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E79" s="10"/>
     </row>
     <row r="80" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B80" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C80" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80" s="9">
-        <v>3</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>278</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E80" s="10"/>
     </row>
     <row r="81" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B81" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" s="9">
         <v>3</v>
       </c>
-      <c r="E81" s="10" t="s">
-        <v>279</v>
-      </c>
+      <c r="E81" s="10"/>
     </row>
     <row r="82" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B82" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C82" s="9">
         <v>0</v>
       </c>
       <c r="D82" s="9">
-        <v>3</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>280</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E82" s="10"/>
     </row>
     <row r="83" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B83" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C83" s="9">
         <v>0</v>
       </c>
       <c r="D83" s="9">
-        <v>3</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>281</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E83" s="10"/>
     </row>
     <row r="84" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
@@ -3164,26 +2549,22 @@
       <c r="D84" s="9">
         <v>4</v>
       </c>
-      <c r="E84" s="10" t="s">
-        <v>282</v>
-      </c>
+      <c r="E84" s="10"/>
     </row>
     <row r="85" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B85" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C85" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" s="9">
-        <v>3</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>283</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E85" s="10"/>
     </row>
     <row r="86" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
@@ -3196,11 +2577,9 @@
         <v>0</v>
       </c>
       <c r="D86" s="9">
-        <v>4</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>284</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E86" s="10"/>
     </row>
     <row r="87" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
@@ -3213,11 +2592,9 @@
         <v>0</v>
       </c>
       <c r="D87" s="9">
-        <v>5</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>285</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E87" s="10"/>
     </row>
     <row r="88" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
@@ -3227,31 +2604,27 @@
         <v>1</v>
       </c>
       <c r="C88" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88" s="9">
-        <v>2</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>286</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E88" s="10"/>
     </row>
     <row r="89" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B89" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" s="9">
         <v>0</v>
       </c>
       <c r="D89" s="9">
-        <v>3</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>287</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E89" s="10"/>
     </row>
     <row r="90" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
@@ -3264,11 +2637,9 @@
         <v>0</v>
       </c>
       <c r="D90" s="9">
-        <v>4</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>288</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E90" s="10"/>
     </row>
     <row r="91" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
@@ -3278,14 +2649,12 @@
         <v>1</v>
       </c>
       <c r="C91" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91" s="9">
         <v>2</v>
       </c>
-      <c r="E91" s="10" t="s">
-        <v>289</v>
-      </c>
+      <c r="E91" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -3310,7 +2679,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="200.6640625" customWidth="1"/>
+    <col min="3" max="3" width="59.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3331,20 +2700,16 @@
       <c r="B2" s="9">
         <v>0</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>290</v>
-      </c>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B3" s="9">
-        <v>1</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>291</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -3353,31 +2718,25 @@
       <c r="B4" s="9">
         <v>0</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>292</v>
-      </c>
+      <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>143</v>
       </c>
       <c r="B5" s="9">
-        <v>1</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>293</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>144</v>
       </c>
       <c r="B6" s="9">
-        <v>1</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>294</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -3386,31 +2745,25 @@
       <c r="B7" s="9">
         <v>1</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>295</v>
-      </c>
+      <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>146</v>
       </c>
       <c r="B8" s="9">
-        <v>1</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>296</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B9" s="9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>297</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C9" s="10"/>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -3419,20 +2772,16 @@
       <c r="B10" s="9">
         <v>0</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>298</v>
-      </c>
+      <c r="C10" s="10"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B11" s="9">
-        <v>1</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>299</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C11" s="10"/>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
@@ -3441,31 +2790,25 @@
       <c r="B12" s="9">
         <v>1</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>300</v>
-      </c>
+      <c r="C12" s="10"/>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B13" s="9">
-        <v>1</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>301</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C13" s="10"/>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>152</v>
       </c>
       <c r="B14" s="9">
-        <v>1</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>302</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C14" s="10"/>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
@@ -3474,20 +2817,16 @@
       <c r="B15" s="9">
         <v>1</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>303</v>
-      </c>
+      <c r="C15" s="10"/>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>154</v>
       </c>
       <c r="B16" s="9">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>304</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C16" s="10"/>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
@@ -3496,31 +2835,25 @@
       <c r="B17" s="9">
         <v>0</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>305</v>
-      </c>
+      <c r="C17" s="10"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>156</v>
       </c>
       <c r="B18" s="9">
-        <v>1</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>306</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C18" s="10"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>157</v>
       </c>
       <c r="B19" s="9">
-        <v>1</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>307</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C19" s="10"/>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
@@ -3529,31 +2862,25 @@
       <c r="B20" s="9">
         <v>1</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>308</v>
-      </c>
+      <c r="C20" s="10"/>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>159</v>
       </c>
       <c r="B21" s="9">
-        <v>1</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>309</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C21" s="10"/>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>160</v>
       </c>
       <c r="B22" s="9">
-        <v>1</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>310</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C22" s="10"/>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
@@ -3562,9 +2889,7 @@
       <c r="B23" s="9">
         <v>1</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>311</v>
-      </c>
+      <c r="C23" s="10"/>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
@@ -3573,9 +2898,7 @@
       <c r="B24" s="9">
         <v>0</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>312</v>
-      </c>
+      <c r="C24" s="10"/>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
@@ -3584,9 +2907,7 @@
       <c r="B25" s="9">
         <v>0</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>313</v>
-      </c>
+      <c r="C25" s="10"/>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
@@ -3595,20 +2916,16 @@
       <c r="B26" s="9">
         <v>0</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>314</v>
-      </c>
+      <c r="C26" s="10"/>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>165</v>
       </c>
       <c r="B27" s="9">
-        <v>0</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>315</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C27" s="10"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
@@ -3617,20 +2934,16 @@
       <c r="B28" s="9">
         <v>0</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>316</v>
-      </c>
+      <c r="C28" s="10"/>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>167</v>
       </c>
       <c r="B29" s="9">
-        <v>1</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>317</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C29" s="10"/>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
@@ -3639,9 +2952,7 @@
       <c r="B30" s="9">
         <v>0</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>318</v>
-      </c>
+      <c r="C30" s="10"/>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
@@ -3650,9 +2961,7 @@
       <c r="B31" s="9">
         <v>1</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>319</v>
-      </c>
+      <c r="C31" s="10"/>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
@@ -3661,20 +2970,16 @@
       <c r="B32" s="9">
         <v>0</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>320</v>
-      </c>
+      <c r="C32" s="10"/>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>171</v>
       </c>
       <c r="B33" s="9">
-        <v>1</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>321</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C33" s="10"/>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
@@ -3683,20 +2988,16 @@
       <c r="B34" s="9">
         <v>1</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>322</v>
-      </c>
+      <c r="C34" s="10"/>
     </row>
     <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>173</v>
       </c>
       <c r="B35" s="9">
-        <v>1</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>323</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C35" s="10"/>
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
@@ -3705,9 +3006,7 @@
       <c r="B36" s="9">
         <v>1</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>324</v>
-      </c>
+      <c r="C36" s="10"/>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
@@ -3716,20 +3015,16 @@
       <c r="B37" s="9">
         <v>1</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>325</v>
-      </c>
+      <c r="C37" s="10"/>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>176</v>
       </c>
       <c r="B38" s="9">
-        <v>0</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>326</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C38" s="10"/>
     </row>
     <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
@@ -3738,9 +3033,7 @@
       <c r="B39" s="9">
         <v>0</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>327</v>
-      </c>
+      <c r="C39" s="10"/>
     </row>
     <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
@@ -3749,9 +3042,7 @@
       <c r="B40" s="9">
         <v>0</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>328</v>
-      </c>
+      <c r="C40" s="10"/>
     </row>
     <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
@@ -3760,9 +3051,7 @@
       <c r="B41" s="9">
         <v>1</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>329</v>
-      </c>
+      <c r="C41" s="10"/>
     </row>
     <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
@@ -3771,9 +3060,7 @@
       <c r="B42" s="9">
         <v>0</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>330</v>
-      </c>
+      <c r="C42" s="10"/>
     </row>
     <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
@@ -3782,9 +3069,7 @@
       <c r="B43" s="9">
         <v>0</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>331</v>
-      </c>
+      <c r="C43" s="10"/>
     </row>
     <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
@@ -3793,9 +3078,7 @@
       <c r="B44" s="9">
         <v>0</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>332</v>
-      </c>
+      <c r="C44" s="10"/>
     </row>
     <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
@@ -3804,9 +3087,7 @@
       <c r="B45" s="9">
         <v>0</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>333</v>
-      </c>
+      <c r="C45" s="10"/>
     </row>
     <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
@@ -3815,20 +3096,16 @@
       <c r="B46" s="9">
         <v>0</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>334</v>
-      </c>
+      <c r="C46" s="10"/>
     </row>
     <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>185</v>
       </c>
       <c r="B47" s="9">
-        <v>0</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>335</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C47" s="10"/>
     </row>
     <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
@@ -3837,20 +3114,16 @@
       <c r="B48" s="9">
         <v>0</v>
       </c>
-      <c r="C48" s="10" t="s">
-        <v>336</v>
-      </c>
+      <c r="C48" s="10"/>
     </row>
     <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>187</v>
       </c>
       <c r="B49" s="9">
-        <v>1</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>337</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C49" s="10"/>
     </row>
     <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
@@ -3859,9 +3132,7 @@
       <c r="B50" s="9">
         <v>0</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>338</v>
-      </c>
+      <c r="C50" s="10"/>
     </row>
     <row r="51" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
@@ -3870,9 +3141,7 @@
       <c r="B51" s="9">
         <v>0</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>339</v>
-      </c>
+      <c r="C51" s="10"/>
     </row>
     <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
@@ -3881,53 +3150,43 @@
       <c r="B52" s="9">
         <v>1</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>340</v>
-      </c>
+      <c r="C52" s="10"/>
     </row>
     <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>191</v>
       </c>
       <c r="B53" s="9">
-        <v>1</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>341</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C53" s="10"/>
     </row>
     <row r="54" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>192</v>
       </c>
       <c r="B54" s="9">
-        <v>1</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>342</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C54" s="10"/>
     </row>
     <row r="55" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>193</v>
       </c>
       <c r="B55" s="9">
-        <v>1</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>343</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C55" s="10"/>
     </row>
     <row r="56" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>194</v>
       </c>
       <c r="B56" s="9">
-        <v>1</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>344</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C56" s="10"/>
     </row>
     <row r="57" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
@@ -3936,9 +3195,7 @@
       <c r="B57" s="9">
         <v>0</v>
       </c>
-      <c r="C57" s="10" t="s">
-        <v>345</v>
-      </c>
+      <c r="C57" s="10"/>
     </row>
     <row r="58" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
@@ -3947,20 +3204,16 @@
       <c r="B58" s="9">
         <v>0</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>346</v>
-      </c>
+      <c r="C58" s="10"/>
     </row>
     <row r="59" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>197</v>
       </c>
       <c r="B59" s="9">
-        <v>1</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>347</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C59" s="10"/>
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
@@ -3969,20 +3222,16 @@
       <c r="B60" s="9">
         <v>1</v>
       </c>
-      <c r="C60" s="10" t="s">
-        <v>348</v>
-      </c>
+      <c r="C60" s="10"/>
     </row>
     <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>199</v>
       </c>
       <c r="B61" s="9">
-        <v>1</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>349</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C61" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
